--- a/artfynd/A 17502-2022 artfynd.xlsx
+++ b/artfynd/A 17502-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17502-2022 artfynd.xlsx
+++ b/artfynd/A 17502-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68328998</v>
+        <v>68573950</v>
       </c>
       <c r="B2" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3624</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1194, Ög</t>
+          <t>Ullstämma Syd - Obj 1193, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540741.0629344035</v>
+        <v>540675</v>
       </c>
       <c r="R2" t="n">
-        <v>6467442.96175745</v>
+        <v>6467525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Barrskog SSV om Hagen. Bestånd 1194 i Linköping kn skogsbruksplan.</t>
+          <t>Barrskog med inslag av löv.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68328993</v>
+        <v>68328998</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,23 +792,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>3624</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540741.0629344035</v>
+        <v>540741</v>
       </c>
       <c r="R3" t="n">
-        <v>6467442.96175745</v>
+        <v>6467443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,21 +845,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>Barrskog SSV om Hagen. Bestånd 1194 i Linköping kn skogsbruksplan.</t>
@@ -905,7 +866,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>barrskogBarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,37 +888,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68573991</v>
+        <v>68328993</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540782.7954447428</v>
+        <v>540741</v>
       </c>
       <c r="R4" t="n">
-        <v>6467374.103464169</v>
+        <v>6467443</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,24 +956,14 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Barrskog med inslag av löv.</t>
+          <t>Barrskog SSV om Hagen. Bestånd 1194 i Linköping kn skogsbruksplan.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,6 +974,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>barrskogBarrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1048,61 +999,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116235007</v>
+        <v>68573991</v>
       </c>
       <c r="B5" t="n">
-        <v>82615</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>252386</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Långfotad murkla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gyromitra splendida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Raitv.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hygge Ullstämma, Ullstämmaskogen, Ög</t>
+          <t>Ullstämma Syd - Obj 1194, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540623</v>
+        <v>540783</v>
       </c>
       <c r="R5" t="n">
-        <v>6467422</v>
+        <v>6467374</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1129,12 +1064,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2014-09-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av löv.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,22 +1083,134 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116235007</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83625</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>252386</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Långfotad murkla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gyromitra splendida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Raitv.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hygge Ullstämma, Ullstämmaskogen, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>540623</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6467422</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Andrejs Petruhins</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Andrejs Petruhins</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17502-2022 artfynd.xlsx
+++ b/artfynd/A 17502-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68573950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68328998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68328993</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68573991</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,8 +1236,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116235007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>